--- a/data/trans_dic/IP16B98-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero otros medicamentos recetados por el médico</t>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -711,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,51; 100,0</t>
+          <t>62,73; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,2; 100,0</t>
+          <t>56,17; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,86; 100,0</t>
+          <t>60,69; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,4; 100,0</t>
+          <t>67,08; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,08; 100,0</t>
+          <t>82,87; 100,0</t>
         </is>
       </c>
     </row>
@@ -796,27 +797,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,31; 100,0</t>
+          <t>42,77; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,99; 100,0</t>
+          <t>48,6; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,49; 100,0</t>
+          <t>55,21; 100,0</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,44; 100,0</t>
+          <t>36,6; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,29; 100,0</t>
+          <t>46,98; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,07; 100,0</t>
+          <t>55,62; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,47; 100,0</t>
+          <t>71,68; 100,0</t>
         </is>
       </c>
     </row>
@@ -951,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,62; 100,0</t>
+          <t>74,38; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,2; 100,0</t>
+          <t>88,45; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,22; 100,0</t>
+          <t>74,58; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,44; 100,0</t>
+          <t>80,27; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,25; 98,26</t>
+          <t>81,86; 97,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,49; 98,77</t>
+          <t>86,74; 98,77</t>
         </is>
       </c>
     </row>
@@ -1001,4 +1002,706 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4857</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5990</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10846</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10290</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5956</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9930</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10058</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18162</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4102; 6538</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2682; 4775</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5430; 8947</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7588; 11313</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>15643; 18877</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1881</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4308</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1897</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2188; 5115</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2526; 5198</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3862; 6996</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3506</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7641</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4474</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11148</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8049</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1511; 4129</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4105; 8738</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6810; 12245</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>6167; 8603</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>15589</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21114</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21576</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36622</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>42690</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12494; 16798</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19164; 21668</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17006; 22803</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>18540; 23098</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>32418; 38513</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>38830; 44216</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B98-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Habitat-trans_dic.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,73; 100,0</t>
+          <t>62,24; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -722,22 +722,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,17; 100,0</t>
+          <t>42,2; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,69; 100,0</t>
+          <t>67,21; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,08; 100,0</t>
+          <t>65,9; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,87; 100,0</t>
+          <t>81,24; 100,0</t>
         </is>
       </c>
     </row>
@@ -807,17 +807,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,77; 100,0</t>
+          <t>42,99; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,6; 100,0</t>
+          <t>51,43; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,21; 100,0</t>
+          <t>54,04; 100,0</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,6; 100,0</t>
+          <t>38,58; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,98; 100,0</t>
+          <t>47,13; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,62; 100,0</t>
+          <t>56,61; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,68; 100,0</t>
+          <t>66,48; 100,0</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,38; 100,0</t>
+          <t>77,57; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,45; 100,0</t>
+          <t>86,8; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -967,17 +967,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,27; 100,0</t>
+          <t>80,45; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,86; 97,25</t>
+          <t>82,03; 97,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,74; 98,77</t>
+          <t>86,6; 98,76</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4102; 6538</t>
+          <t>4070; 6538</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1310,22 +1310,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2682; 4775</t>
+          <t>2015; 4775</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5430; 8947</t>
+          <t>6013; 8947</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7588; 11313</t>
+          <t>7456; 11313</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15643; 18877</t>
+          <t>15335; 18877</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2188; 5115</t>
+          <t>2199; 5115</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2526; 5198</t>
+          <t>2673; 5198</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3862; 6996</t>
+          <t>3781; 6996</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1511; 4129</t>
+          <t>1593; 4129</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4105; 8738</t>
+          <t>4118; 8738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6810; 12245</t>
+          <t>6932; 12245</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6167; 8603</t>
+          <t>5719; 8603</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12494; 16798</t>
+          <t>13030; 16798</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19164; 21668</t>
+          <t>18807; 21668</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17006; 22803</t>
+          <t>17007; 22803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18540; 23098</t>
+          <t>18582; 23098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32418; 38513</t>
+          <t>32484; 38602</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38830; 44216</t>
+          <t>38766; 44211</t>
         </is>
       </c>
     </row>
